--- a/family_tree_synthetic.xlsx
+++ b/family_tree_synthetic.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visvel\Downloads\family_tree_project\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AF1ED6-96BF-49F6-9576-1E4DC0B4D9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>Unique ID</t>
   </si>
@@ -46,24 +52,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Alex</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Jane</t>
-  </si>
-  <si>
-    <t>Robert</t>
-  </si>
-  <si>
-    <t>Emily</t>
-  </si>
-  <si>
-    <t>Kevin</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -73,12 +61,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>4;5</t>
-  </si>
-  <si>
     <t>1980-05-01</t>
   </si>
   <si>
@@ -119,13 +101,34 @@
   </si>
   <si>
     <t>Occupation: Doctor</t>
+  </si>
+  <si>
+    <t>viswanath</t>
+  </si>
+  <si>
+    <t>vellaiappn</t>
+  </si>
+  <si>
+    <t>shanthi</t>
+  </si>
+  <si>
+    <t>nivetha</t>
+  </si>
+  <si>
+    <t>shivani</t>
+  </si>
+  <si>
+    <t>amarnath</t>
+  </si>
+  <si>
+    <t>22;5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,13 +191,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +243,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -266,6 +277,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -300,9 +312,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -475,11 +488,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,157 +524,160 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>22</v>
       </c>
       <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
       <c r="J2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" t="s">
-        <v>30</v>
-      </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>19</v>
       </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
         <v>18</v>
       </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/family_tree_synthetic.xlsx
+++ b/family_tree_synthetic.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visvel\Downloads\family_tree_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visvel\Downloads\family_tree_project\family_tree_d3_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AF1ED6-96BF-49F6-9576-1E4DC0B4D9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45BC383-84DE-4BC5-9A19-5AF8AF394CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
   <si>
     <t>Unique ID</t>
   </si>
@@ -52,33 +52,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1980-05-01</t>
-  </si>
-  <si>
-    <t>1950-06-12</t>
-  </si>
-  <si>
-    <t>1952-07-23</t>
-  </si>
-  <si>
-    <t>1981-03-22</t>
-  </si>
-  <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
-    <t>2002-12-12</t>
-  </si>
-  <si>
     <t>Valavu A</t>
   </si>
   <si>
@@ -88,9 +61,6 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>Occupation: Engineer</t>
   </si>
   <si>
@@ -109,6 +79,12 @@
     <t>vellaiappn</t>
   </si>
   <si>
+    <t>22;5</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>shanthi</t>
   </si>
   <si>
@@ -119,9 +95,6 @@
   </si>
   <si>
     <t>amarnath</t>
-  </si>
-  <si>
-    <t>22;5</t>
   </si>
 </sst>
 </file>
@@ -180,11 +153,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,31 +503,31 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2">
+        <v>29342</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -561,25 +535,25 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2">
+        <v>18426</v>
+      </c>
+      <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -587,25 +561,25 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2">
+        <v>19198</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" t="s">
         <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -613,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>22</v>
@@ -621,17 +595,17 @@
       <c r="F5">
         <v>4</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="2">
+        <v>29667</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
         <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -639,7 +613,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>22</v>
@@ -647,14 +621,14 @@
       <c r="D6">
         <v>3</v>
       </c>
-      <c r="G6" t="s">
-        <v>17</v>
+      <c r="G6" s="2">
+        <v>36526</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -662,7 +636,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -670,14 +644,14 @@
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="G7" t="s">
-        <v>18</v>
+      <c r="G7" s="2">
+        <v>37602</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/family_tree_synthetic.xlsx
+++ b/family_tree_synthetic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visvel\Downloads\family_tree_project\family_tree_d3_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45BC383-84DE-4BC5-9A19-5AF8AF394CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F438D2-3FDF-48F4-B698-850BDC6559F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="17280" windowHeight="10665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
   <si>
     <t>Unique ID</t>
   </si>
@@ -95,6 +95,15 @@
   </si>
   <si>
     <t>amarnath</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -463,10 +472,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,183 +483,204 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>22</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>4</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>29342</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="E3">
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3">
         <v>2</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>18426</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>11</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>20</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="E4">
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>19198</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>11</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>20</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="E5">
+      <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
         <v>22</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>4</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>29667</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>10</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>12</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6">
         <v>22</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>36526</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>10</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>37602</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>10</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/family_tree_synthetic.xlsx
+++ b/family_tree_synthetic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visvel\Downloads\family_tree_project\family_tree_d3_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F438D2-3FDF-48F4-B698-850BDC6559F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8ECC2A-9547-4C73-8E8B-634843EF9A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="23280" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>Unique ID</t>
   </si>
@@ -104,6 +104,54 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>swaminathan</t>
+  </si>
+  <si>
+    <t>bagirathi</t>
+  </si>
+  <si>
+    <t>subramanium</t>
+  </si>
+  <si>
+    <t>deivanayagi</t>
+  </si>
+  <si>
+    <t>1;10</t>
+  </si>
+  <si>
+    <t>2;11</t>
+  </si>
+  <si>
+    <t>venu</t>
+  </si>
+  <si>
+    <t>nadu</t>
+  </si>
+  <si>
+    <t>latha</t>
+  </si>
+  <si>
+    <t>punitha</t>
+  </si>
+  <si>
+    <t>14;15</t>
+  </si>
+  <si>
+    <t>16;17</t>
+  </si>
+  <si>
+    <t>Nishanth</t>
+  </si>
+  <si>
+    <t>Niveth</t>
+  </si>
+  <si>
+    <t>Ponni</t>
+  </si>
+  <si>
+    <t>Shanthosh</t>
   </si>
 </sst>
 </file>
@@ -472,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -555,6 +603,12 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
       <c r="F3">
         <v>2</v>
       </c>
@@ -584,6 +638,12 @@
       <c r="C4" t="s">
         <v>27</v>
       </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
@@ -682,6 +742,228 @@
       </c>
       <c r="J7" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+      <c r="F13">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15">
+        <v>11</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17">
+        <v>10</v>
+      </c>
+      <c r="E17">
+        <v>12</v>
+      </c>
+      <c r="K17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18">
+        <v>11</v>
+      </c>
+      <c r="E18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
